--- a/catering_order_forms/011_tournament_catering_service_order_form--catering_order_forms.xlsx
+++ b/catering_order_forms/011_tournament_catering_service_order_form--catering_order_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -441,9 +441,9 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="6" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="36" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -520,15 +520,19 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>tournament_details</t>
+          <t>name</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>tournament_details</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr"/>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Full name of the client</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
           <t>no</t>
@@ -543,64 +547,76 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>contact_details</t>
+          <t>email</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>contact_details</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr"/>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Email of the client</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>contact_details</t>
+          <t>event_date</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>contact_details</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr"/>
+          <t>Event Date</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Date of the event</t>
+        </is>
+      </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>time</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>contact_details</t>
+          <t>event_time</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>contact_details</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr"/>
+          <t>Event Time</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Time of the event</t>
+        </is>
+      </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -612,15 +628,19 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>event_details</t>
+          <t>event_duration</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>event_details</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr"/>
+          <t>Event Duration</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Duration of the event</t>
+        </is>
+      </c>
       <c r="E8" t="inlineStr">
         <is>
           <t>no</t>
@@ -630,66 +650,78 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>event_details</t>
+          <t>event_location</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>event_details</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr"/>
+          <t>Event Location</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Location of the event</t>
+        </is>
+      </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>event_details</t>
+          <t>catering_preferences</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>event_details</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr"/>
+          <t>Catering Preferences</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Do you need catering services?</t>
+        </is>
+      </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>event_details</t>
+          <t>catering_choices</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>event_details</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
+          <t>Catering Choices</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Select your catering preferences</t>
+        </is>
+      </c>
       <c r="E11" t="inlineStr">
         <is>
           <t>no</t>
@@ -699,20 +731,24 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>event_details</t>
+          <t>num_guests</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>event_details</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
+          <t>Number of Guests</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Number of guests</t>
+        </is>
+      </c>
       <c r="E12" t="inlineStr">
         <is>
           <t>no</t>
@@ -722,20 +758,24 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>event_details</t>
+          <t>special_requests</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>event_details</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
+          <t>Special Requests</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Any special requests?</t>
+        </is>
+      </c>
       <c r="E13" t="inlineStr">
         <is>
           <t>no</t>
@@ -750,15 +790,19 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>catering_details</t>
+          <t>contact_name</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>catering_details</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
+          <t>Contact Name</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Name of the contact person</t>
+        </is>
+      </c>
       <c r="E14" t="inlineStr">
         <is>
           <t>no</t>
@@ -773,15 +817,19 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>catering_details</t>
+          <t>contact_phone</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>catering_details</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
+          <t>Contact Phone</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Phone number of the contact person</t>
+        </is>
+      </c>
       <c r="E15" t="inlineStr">
         <is>
           <t>no</t>
@@ -796,15 +844,19 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>catering_details</t>
+          <t>contact_email</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>catering_details</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
+          <t>Contact Email</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Email of the contact person</t>
+        </is>
+      </c>
       <c r="E16" t="inlineStr">
         <is>
           <t>no</t>
@@ -819,15 +871,19 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>catering_details</t>
+          <t>contact_message</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>catering_details</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
+          <t>Contact Message</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Any message to the contact person</t>
+        </is>
+      </c>
       <c r="E17" t="inlineStr">
         <is>
           <t>no</t>
@@ -842,15 +898,19 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>catering_details</t>
+          <t>event_type</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>catering_details</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
+          <t>Event Type</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Type of event</t>
+        </is>
+      </c>
       <c r="E18" t="inlineStr">
         <is>
           <t>no</t>
@@ -865,15 +925,19 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>catering_details</t>
+          <t>special_requests_2</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>catering_details</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
+          <t>Special Requests 2</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Any other special requests</t>
+        </is>
+      </c>
       <c r="E19" t="inlineStr">
         <is>
           <t>no</t>
@@ -888,18 +952,22 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>catering_details</t>
+          <t>confirm</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>catering_details</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
+          <t>Confirm</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Please confirm your event details</t>
+        </is>
+      </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -914,12 +982,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C5"/>
+  <dimension ref="A1:C8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="23" customWidth="1" min="1" max="1"/>
-    <col width="6" customWidth="1" min="2" max="2"/>
-    <col width="7" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -942,7 +1010,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>event_details_choices</t>
+          <t>catering_preferences_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -959,7 +1027,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>event_details_choices</t>
+          <t>catering_preferences_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -976,34 +1044,85 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>event_details_choices</t>
+          <t>catering_choices_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>menu_1</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Menu 1</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>event_details_choices</t>
+          <t>catering_choices_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>menu_2</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Menu 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>catering_choices_choices</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>menu_3</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Menu 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>catering_choices_choices</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>menu_4</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Menu 4</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>catering_choices_choices</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>menu_5</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Menu 5</t>
         </is>
       </c>
     </row>
